--- a/output_3a_153330.xlsx
+++ b/output_3a_153330.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/920f25d3c1adf657/Projects/Test2/Advanced-PM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_4DCF086B060D7E568B224F0748C4A0FBDE395D76" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{15AEEACD-3F9A-4CEA-8159-332053EDF7AF}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_4DCF086B060D7E568B224F0748C4A0FBDE395D76" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D82B4024-02D5-4D2A-8617-5C1247878AE1}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Production Plan" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,20 @@
     <sheet name="Overtime Plan" sheetId="4" r:id="rId4"/>
     <sheet name="Cost Summary" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
